--- a/data/trans_dic/IP12B$garganta-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57,41; 95,13</t>
+          <t>57,13; 95,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,44; 61,74</t>
+          <t>25,76; 62,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,11; 85,73</t>
+          <t>47,16; 85,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,14; 70,41</t>
+          <t>15,49; 71,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,68; 64,88</t>
+          <t>18,63; 65,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 56,99</t>
+          <t>6,89; 56,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,13; 79,06</t>
+          <t>41,13; 76,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,99; 57,02</t>
+          <t>27,01; 56,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,4; 68,4</t>
+          <t>34,04; 69,0</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,05; 74,48</t>
+          <t>38,74; 75,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,92; 77,84</t>
+          <t>42,12; 78,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,93; 48,66</t>
+          <t>18,03; 48,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,17; 59,07</t>
+          <t>27,12; 61,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,66; 76,78</t>
+          <t>43,65; 76,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,01; 73,29</t>
+          <t>34,91; 72,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,52; 60,61</t>
+          <t>33,71; 61,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,23; 72,31</t>
+          <t>48,41; 72,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,15; 54,12</t>
+          <t>29,72; 54,63</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,13; 67,95</t>
+          <t>21,13; 69,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 55,39</t>
+          <t>14,6; 57,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,83; 76,75</t>
+          <t>30,52; 77,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,51; 92,27</t>
+          <t>38,96; 91,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,92; 84,88</t>
+          <t>32,69; 82,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,53; 61,95</t>
+          <t>17,99; 62,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,57; 75,01</t>
+          <t>38,24; 74,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,69; 64,02</t>
+          <t>29,59; 62,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,26; 63,73</t>
+          <t>30,78; 62,03</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 74,84</t>
+          <t>17,04; 75,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,15; 92,79</t>
+          <t>40,8; 92,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 71,07</t>
+          <t>16,09; 72,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 65,79</t>
+          <t>8,39; 65,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,29; 42,14</t>
+          <t>8,61; 42,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,98; 83,84</t>
+          <t>27,78; 84,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,12; 59,58</t>
+          <t>20,19; 58,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,76; 56,8</t>
+          <t>25,5; 57,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,99; 70,1</t>
+          <t>28,42; 69,02</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,51; 67,85</t>
+          <t>44,01; 68,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,82; 62,53</t>
+          <t>41,34; 61,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,69; 57,21</t>
+          <t>36,39; 58,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35,85; 58,92</t>
+          <t>34,77; 57,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,07; 58,52</t>
+          <t>36,72; 57,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,32; 57,36</t>
+          <t>33,47; 57,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,54; 58,98</t>
+          <t>42,59; 59,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,96; 56,64</t>
+          <t>41,8; 56,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,2; 53,8</t>
+          <t>38,53; 53,84</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7551</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7621</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8182</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3976</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5160</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>11527</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>12781</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9955</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5217; 8696</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4627; 11179</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5596; 10179</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1444; 6662</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2465; 8699</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>509; 4188</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7590; 14166</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8426; 17514</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>6556; 13290</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8989</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12524</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7379</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8138</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15292</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9880</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17126</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>27815</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>17259</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6221; 12139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8525; 15899</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4096; 11098</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5322; 12150</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10964; 19223</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6370; 13162</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12028; 21879</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>21957; 32793</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12175; 22383</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4873</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7056</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6158</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5524</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>11683</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>11031</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11975</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2270; 7515</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2045; 8073</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3671; 9289</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3883; 9105</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3342; 8434</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2526; 8715</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7920; 15521</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7171; 15192</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>8025; 16173</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3384</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6388</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3536</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3319</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4629</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9708</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8165</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1354; 6003</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3702; 8390</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1369; 6160</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>654; 5101</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1290; 6313</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2270; 6903</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3177; 9206</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6135; 13779</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4741; 11512</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>24550</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31407</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>25548</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29929</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21805</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46267</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>61336</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>47354</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>19310; 29995</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25338; 37976</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20062; 32430</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16241; 26946</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23341; 36335</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>16019; 27576</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>38578; 53788</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>52194; 70015</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>39679; 55447</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$garganta-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57,13; 95,23</t>
+          <t>58,12; 97,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,76; 62,23</t>
+          <t>24,79; 61,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,16; 85,79</t>
+          <t>44,4; 87,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 71,46</t>
+          <t>20,13; 71,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 65,73</t>
+          <t>19,33; 64,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 56,63</t>
+          <t>7,23; 56,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,13; 76,76</t>
+          <t>41,18; 77,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,01; 56,14</t>
+          <t>26,09; 57,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,04; 69,0</t>
+          <t>34,21; 68,56</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,74; 75,6</t>
+          <t>35,96; 74,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,12; 78,54</t>
+          <t>42,08; 77,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,03; 48,84</t>
+          <t>19,16; 47,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,12; 61,92</t>
+          <t>24,57; 61,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,65; 76,53</t>
+          <t>42,6; 76,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,91; 72,13</t>
+          <t>35,33; 72,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,71; 61,32</t>
+          <t>35,02; 61,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,41; 72,3</t>
+          <t>48,48; 72,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,72; 54,63</t>
+          <t>30,41; 55,09</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,13; 69,96</t>
+          <t>21,44; 70,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 57,62</t>
+          <t>15,09; 56,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,52; 77,23</t>
+          <t>29,02; 73,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,96; 91,34</t>
+          <t>42,03; 91,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,69; 82,51</t>
+          <t>34,38; 82,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,99; 62,06</t>
+          <t>17,91; 66,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,24; 74,94</t>
+          <t>36,63; 73,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,59; 62,69</t>
+          <t>30,06; 63,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,78; 62,03</t>
+          <t>29,58; 63,28</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 75,56</t>
+          <t>16,85; 74,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,8; 92,47</t>
+          <t>38,98; 92,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 72,39</t>
+          <t>15,51; 71,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 65,46</t>
+          <t>8,36; 65,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 42,12</t>
+          <t>8,56; 44,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,78; 84,49</t>
+          <t>27,81; 84,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 58,5</t>
+          <t>20,7; 58,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,5; 57,27</t>
+          <t>25,4; 56,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,42; 69,02</t>
+          <t>29,32; 71,48</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,01; 68,36</t>
+          <t>44,04; 68,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,34; 61,96</t>
+          <t>41,12; 62,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,39; 58,83</t>
+          <t>36,33; 56,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,77; 57,69</t>
+          <t>33,93; 58,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,72; 57,17</t>
+          <t>36,04; 57,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,47; 57,62</t>
+          <t>33,87; 57,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,59; 59,38</t>
+          <t>43,1; 60,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,8; 56,08</t>
+          <t>42,14; 56,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,53; 53,84</t>
+          <t>37,95; 53,78</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5217; 8696</t>
+          <t>5307; 8937</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4627; 11179</t>
+          <t>4453; 10960</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5596; 10179</t>
+          <t>5269; 10417</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1444; 6662</t>
+          <t>1877; 6656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2465; 8699</t>
+          <t>2558; 8558</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>509; 4188</t>
+          <t>535; 4173</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7590; 14166</t>
+          <t>7600; 14382</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8426; 17514</t>
+          <t>8139; 17901</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6556; 13290</t>
+          <t>6590; 13205</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6221; 12139</t>
+          <t>5775; 12033</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8525; 15899</t>
+          <t>8518; 15772</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4096; 11098</t>
+          <t>4352; 10873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5322; 12150</t>
+          <t>4822; 12066</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10964; 19223</t>
+          <t>10701; 19110</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6370; 13162</t>
+          <t>6447; 13310</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12028; 21879</t>
+          <t>12496; 21812</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21957; 32793</t>
+          <t>21991; 33070</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12175; 22383</t>
+          <t>12460; 22572</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2270; 7515</t>
+          <t>2303; 7562</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2045; 8073</t>
+          <t>2115; 7846</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3671; 9289</t>
+          <t>3490; 8885</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3883; 9105</t>
+          <t>4190; 9139</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3342; 8434</t>
+          <t>3514; 8429</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2526; 8715</t>
+          <t>2515; 9269</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7920; 15521</t>
+          <t>7586; 15140</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7171; 15192</t>
+          <t>7285; 15278</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8025; 16173</t>
+          <t>7712; 16499</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1354; 6003</t>
+          <t>1338; 5934</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3702; 8390</t>
+          <t>3537; 8395</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1369; 6160</t>
+          <t>1320; 6076</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>654; 5101</t>
+          <t>651; 5123</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1290; 6313</t>
+          <t>1284; 6598</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2270; 6903</t>
+          <t>2272; 6903</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3177; 9206</t>
+          <t>3257; 9247</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6135; 13779</t>
+          <t>6111; 13506</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4741; 11512</t>
+          <t>4890; 11923</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19310; 29995</t>
+          <t>19323; 29890</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25338; 37976</t>
+          <t>25203; 38201</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20062; 32430</t>
+          <t>20027; 31390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16241; 26946</t>
+          <t>15846; 27115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23341; 36335</t>
+          <t>22908; 36394</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16019; 27576</t>
+          <t>16210; 27319</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38578; 53788</t>
+          <t>39041; 54428</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52194; 70015</t>
+          <t>52614; 70406</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39679; 55447</t>
+          <t>39078; 55388</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$garganta-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42,65%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38,99%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23,98%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>82,69%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>42,42%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>68,95%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42,65%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,12; 97,87</t>
+          <t>18,14; 70,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,79; 61,01</t>
+          <t>17,68; 64,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,4; 87,79</t>
+          <t>7,0; 56,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 71,39</t>
+          <t>57,41; 95,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,33; 64,67</t>
+          <t>23,44; 61,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 56,43</t>
+          <t>43,11; 85,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,18; 77,93</t>
+          <t>43,13; 79,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,09; 57,38</t>
+          <t>25,99; 57,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,21; 68,56</t>
+          <t>33,4; 68,4</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>41,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60,88%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>55,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>61,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>32,48%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>60,88%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>54,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,96; 74,93</t>
+          <t>24,17; 59,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,08; 77,92</t>
+          <t>42,66; 76,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,16; 47,85</t>
+          <t>35,01; 73,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,57; 61,49</t>
+          <t>36,05; 74,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,6; 76,08</t>
+          <t>41,92; 77,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,33; 72,94</t>
+          <t>17,93; 48,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,02; 61,14</t>
+          <t>32,52; 60,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,48; 72,91</t>
+          <t>49,23; 72,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,41; 55,09</t>
+          <t>30,15; 54,12</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70,79%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>60,25%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39,33%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>43,06%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>34,78%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>53,64%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>70,79%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>60,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,44; 70,39</t>
+          <t>43,51; 92,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 56,0</t>
+          <t>32,92; 84,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,02; 73,87</t>
+          <t>17,53; 61,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,03; 91,68</t>
+          <t>21,13; 67,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,38; 82,45</t>
+          <t>14,9; 55,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 66,0</t>
+          <t>29,83; 76,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,63; 73,1</t>
+          <t>37,57; 75,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,06; 63,05</t>
+          <t>29,69; 64,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,58; 63,28</t>
+          <t>30,26; 63,73</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56,66%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>42,59%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>70,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>41,55%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 74,69</t>
+          <t>8,3; 65,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,98; 92,52</t>
+          <t>8,29; 42,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,51; 71,41</t>
+          <t>25,98; 83,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 65,73</t>
+          <t>17,08; 74,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 44,03</t>
+          <t>41,15; 92,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,81; 84,49</t>
+          <t>13,64; 71,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,7; 58,76</t>
+          <t>21,12; 59,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,4; 56,13</t>
+          <t>23,76; 56,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,32; 71,48</t>
+          <t>29,99; 70,1</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>55,95%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>51,24%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>46,35%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46,5%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,04; 68,12</t>
+          <t>35,85; 58,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,12; 62,33</t>
+          <t>38,07; 58,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,33; 56,94</t>
+          <t>33,32; 57,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,93; 58,05</t>
+          <t>43,51; 67,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,04; 57,26</t>
+          <t>41,82; 62,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,87; 57,08</t>
+          <t>35,69; 57,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,1; 60,09</t>
+          <t>42,54; 58,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>42,14; 56,39</t>
+          <t>41,96; 56,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>37,95; 53,78</t>
+          <t>38,2; 53,8</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3976</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5160</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>7551</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>7621</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>8182</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3976</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5160</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5307; 8937</t>
+          <t>1691; 6564</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4453; 10960</t>
+          <t>2340; 8586</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5269; 10417</t>
+          <t>518; 4214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1877; 6656</t>
+          <t>5242; 8687</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2558; 8558</t>
+          <t>4211; 11092</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>535; 4173</t>
+          <t>5116; 10173</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7600; 14382</t>
+          <t>7959; 14590</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8139; 17901</t>
+          <t>8108; 17790</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6590; 13205</t>
+          <t>6433; 13175</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8138</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15292</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9880</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8989</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>12524</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7379</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8138</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15292</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9880</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5775; 12033</t>
+          <t>4742; 11592</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8518; 15772</t>
+          <t>10715; 19284</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4352; 10873</t>
+          <t>6388; 13373</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4822; 12066</t>
+          <t>5789; 11960</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10701; 19110</t>
+          <t>8485; 15756</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6447; 13310</t>
+          <t>4074; 11056</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12496; 21812</t>
+          <t>11604; 21625</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21991; 33070</t>
+          <t>22329; 32801</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12460; 22572</t>
+          <t>12352; 22171</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7056</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6158</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5524</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>4626</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>4873</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6451</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7056</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6158</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5524</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2303; 7562</t>
+          <t>4337; 9197</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2115; 7846</t>
+          <t>3365; 8677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3490; 8885</t>
+          <t>2462; 8700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4190; 9139</t>
+          <t>2270; 7300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3514; 8429</t>
+          <t>2088; 7761</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2515; 9269</t>
+          <t>3588; 9232</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7586; 15140</t>
+          <t>7780; 15535</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7285; 15278</t>
+          <t>7195; 15515</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7712; 16499</t>
+          <t>7890; 16615</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3319</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4629</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3384</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>6388</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3536</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2546</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3319</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1338; 5934</t>
+          <t>647; 5127</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3537; 8395</t>
+          <t>1243; 6316</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1320; 6076</t>
+          <t>2123; 6850</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>651; 5123</t>
+          <t>1357; 5946</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1284; 6598</t>
+          <t>3734; 8420</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2272; 6903</t>
+          <t>1161; 6047</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3257; 9247</t>
+          <t>3324; 9377</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6111; 13506</t>
+          <t>5718; 13668</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4890; 11923</t>
+          <t>5003; 11692</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29929</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21805</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>24550</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>31407</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>25548</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21716</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>29929</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21805</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19323; 29890</t>
+          <t>16742; 27521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25203; 38201</t>
+          <t>24197; 37194</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20027; 31390</t>
+          <t>15946; 27450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15846; 27115</t>
+          <t>19092; 29770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>22908; 36394</t>
+          <t>25632; 38324</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16210; 27319</t>
+          <t>19674; 31540</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39041; 54428</t>
+          <t>38531; 53426</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52614; 70406</t>
+          <t>52393; 70713</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39078; 55388</t>
+          <t>39342; 55408</t>
         </is>
       </c>
     </row>
